--- a/output_plant/stomata_Intermediate_liang_2022b.xlsx
+++ b/output_plant/stomata_Intermediate_liang_2022b.xlsx
@@ -609,7 +609,7 @@
     <t xml:space="preserve">10.1016/j.revpalbo.2022.104743</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-franks_liang_2022b.xlsx</t>
+    <t xml:space="preserve">stomata-franks_liang_2022b_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>

--- a/output_plant/stomata_Intermediate_liang_2022b.xlsx
+++ b/output_plant/stomata_Intermediate_liang_2022b.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
   <si>
     <t>eDab</t>
   </si>
@@ -643,6 +643,9 @@
   </si>
   <si>
     <t xml:space="preserve">generic value from Franks et al. (2014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source used fixed photosynthesis (fixed_A=yes); A0 is the reported net photosynthetic rate.</t>
   </si>
   <si>
     <t xml:space="preserve">Metasequoia ELS-18-181</t>
@@ -2145,11 +2148,13 @@
       <c r="BJ5" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="BK5" s="1"/>
+      <c r="BK5" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>197</v>
@@ -2326,11 +2331,13 @@
       <c r="BJ6" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="BK6" s="1"/>
+      <c r="BK6" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>197</v>
@@ -2507,11 +2514,13 @@
       <c r="BJ7" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="BK7" s="1"/>
+      <c r="BK7" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>197</v>
@@ -2541,13 +2550,13 @@
         <v>201</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>203</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P8" s="26" t="n">
         <v>83103930</v>
@@ -2632,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="AR8" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AS8" s="1" t="n">
         <v>2</v>
@@ -2688,11 +2697,13 @@
       <c r="BJ8" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="BK8" s="1"/>
+      <c r="BK8" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>197</v>
@@ -2722,13 +2733,13 @@
         <v>201</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>203</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P9" s="26" t="n">
         <v>95937660</v>
@@ -2813,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="AR9" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AS9" s="1" t="n">
         <v>2</v>
@@ -2869,11 +2880,13 @@
       <c r="BJ9" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="BK9" s="1"/>
+      <c r="BK9" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>197</v>
@@ -2903,13 +2916,13 @@
         <v>201</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>203</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P10" s="26" t="n">
         <v>65465200</v>
@@ -2994,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="AR10" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AS10" s="1" t="n">
         <v>2</v>
@@ -3050,7 +3063,9 @@
       <c r="BJ10" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="BK10" s="1"/>
+      <c r="BK10" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
